--- a/eval/error_analysis/results/analysis_by_qid.xlsx
+++ b/eval/error_analysis/results/analysis_by_qid.xlsx
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -9835,7 +9835,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -10493,7 +10493,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -10689,7 +10689,7 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -10797,7 +10797,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -12383,7 +12383,7 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -12409,7 +12409,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -13305,7 +13305,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
@@ -13481,7 +13481,7 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -14835,7 +14835,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -15933,7 +15933,7 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -16657,7 +16657,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         </is>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -17829,7 +17829,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         </is>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -18269,7 +18269,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
@@ -19927,7 +19927,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -21603,7 +21603,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -22715,7 +22715,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -22863,7 +22863,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -23567,7 +23567,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -23785,7 +23785,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -24613,7 +24613,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -25157,7 +25157,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -25353,7 +25353,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         </is>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -26243,7 +26243,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>

--- a/eval/error_analysis/results/analysis_by_qid.xlsx
+++ b/eval/error_analysis/results/analysis_by_qid.xlsx
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -14601,7 +14601,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -14925,7 +14925,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         </is>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -17885,7 +17885,7 @@
         </is>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -22999,7 +22999,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
@@ -23501,7 +23501,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>

--- a/eval/error_analysis/results/analysis_by_qid.xlsx
+++ b/eval/error_analysis/results/analysis_by_qid.xlsx
@@ -18433,7 +18433,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         </is>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -25211,7 +25211,7 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
@@ -25959,7 +25959,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         </is>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">

--- a/eval/error_analysis/results/analysis_by_qid.xlsx
+++ b/eval/error_analysis/results/analysis_by_qid.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T121"/>
+  <dimension ref="A1:T151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,9 +1343,13 @@
       <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5603,9 +5607,13 @@
       <c r="R63" t="n">
         <v>1</v>
       </c>
-      <c r="S63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -6173,9 +6181,13 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -6497,9 +6509,13 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -10353,6 +10369,2378 @@
         </is>
       </c>
       <c r="T121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>40391923</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>40400229</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports genotypic viral resistance profiles for participants who seroconverted.</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples. Genotypic viral resistance profiles were available for 47 of the participants who seroconverted.</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>1</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>40431710</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences obtained from the patient’s samples.</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R124" t="n">
+        <v>1</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>40431742</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from 1667 ART-naive patient samples.</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples. Specifically, it states that "Samples from 1667 PLWHA were analyzed".</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>40490983</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Yes, the paper mentions that sequences for only 83 participants were available, and all participants had genotyping performed.</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>40573423</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Yes, the paper includes HIV sequences from patient samples, stating, 'HIV-1 Genetic Diversity and Transmitted Drug Resistance Mutations in ART-Naive Individuals in South Korea from 2021 to 2024' and 'The genotypes of 487 PWH diagnosed from 2021 to 2024 were analyzed.'</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>40596906</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from 15 mother-child pairs.</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>40713598</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>HIV drug resistance (HIVDR) was retrospectively characterized among 20 children and adolescents with HIV with virologic failure on non-nucleoside reverse transcriptase inhibitor (NNRTI)-based therapy, and virologic response in those switched to dolutegravir (DTG)-based therapy described.</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>40763144</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples. Specifically, it details the mutations found in the HIV genomes of participants who underwent HIV drug resistance testing.</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R130" t="n">
+        <v>1</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>40779404</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences derived from patient samples, specifically historical genotypes and baseline proviral DNA sequencing data.</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV-1 sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R131" t="n">
+        <v>1</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>40839365</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>1</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>40857111</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV-1 resistance results and genotypic/phenotypic resistance analyses based on HIV-1 sequences from patient samples. Specifically, it mentions the inclusion of genotyping data for protease (PR), reverse transcriptase (RT), and integrase (IN) genes from participants with virologic failure and others during the study.</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>40872801</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Yes the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R134" t="n">
+        <v>1</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>40938120</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples, with a total of 1,048 sequences analyzed.</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>40938996</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="n">
+        <v>1</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>40965168</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from 24 patient samples.</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV-1 sequences from patient plasma samples.</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>40974886</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Yes, the paper includes historical RNA or proviral DNA genotype reports from participant samples.</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Yes, HIV-1 sequences from patient samples were reported.</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>41004608</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>1</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R139" t="n">
+        <v>1</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>41012586</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Yes (Only past sequences)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>No, the study does not report HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R140" t="n">
+        <v>1</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>41023944</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Yes, the study included HIV-positive individuals on DTG-based ART who underwent genotypic resistance testing after confirmed virological failure, indicating that HIV sequences were obtained from patient samples.</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>1</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R141" t="n">
+        <v>1</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>41029850</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>41056006</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Yes, the study reported HIV-1 capsid genotypic and phenotypic data at study entry using the GenoSure Gag-Pro and PhenoSense Gag-Pro assays.</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>41057785</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences obtained from patient samples.</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Yes, the paper discusses drug resistance mutations in HIV reported from patient samples.</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>1</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R144" t="n">
+        <v>1</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>41088231</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences obtained from a patient sample (230794) in Guangdong, China.</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples, specifically from individual 230794.</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>41091504</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Yes, the paper discusses the presence of drug-resistant sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>No, the paper does not report HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="n">
+        <v>1</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>41093949</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>No (Published sequences only)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>The sequences generated during the current study are available in the NCBI repository, PQ735970-PQ735985. Additional data are available in the supplementary material.</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>41112839</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples, specifically 131 sequences were successfully amplified and sequenced.</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R148" t="n">
+        <v>1</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>41129268</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from 333 patient samples.</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>41130593</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV sequences from patient samples.</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Yes.</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R150" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>41140464</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Yes, the paper reports HIV-1 pol gene sequences obtained from East African countries.</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>No, the paper does not report sequences from patient samples as it employs a meta-analysis approach using publicly available data from the Los Alamos HIV database.</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10367,7 +12755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T121"/>
+  <dimension ref="A1:T151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11283,9 +13671,13 @@
       <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -11553,7 +13945,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Full length Genome, Gag, Pol, RT</t>
+          <t>Gag, Pol, RT</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -15527,9 +17919,13 @@
       <c r="R63" t="n">
         <v>1</v>
       </c>
-      <c r="S63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Pol</t>
+        </is>
+      </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -16089,9 +18485,13 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -16409,9 +18809,13 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Pol</t>
+        </is>
+      </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -19028,7 +21432,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PR, RT, In</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -20095,7 +22499,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env, Nef, vpu</t>
+          <t>Gag, Pol, Env, Vpu</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -20237,6 +22641,2398 @@
         </is>
       </c>
       <c r="T121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>40391923</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>The genes sequenced included integrase (IN) and protease/reverse transcriptase (PR/RT) regions.</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>The genes sequenced were integrase (IN) and protease/reverse transcriptase (PR/RT) regions.</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>IN, PR, RT</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Integrase, PR/RT</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>IN, PR, RT</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Integrase (IN), Protease (PR), and Reverse transcriptase (RT).</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>PR, RT, and IN</t>
+        </is>
+      </c>
+      <c r="T122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>40400229</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RT,IN</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>The paper reports sequencing of the reverse transcriptase and integrase genes.</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>The paper mentions the M184I/V and K103Q mutations in HIV genes, indicating sequencing of the reverse transcriptase gene for K103Q and protease for M184I.</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Protease, Reverse transcriptase</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Not reported.</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>40431710</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RT, PR, IN</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>The sequenced genes included those associated with resistance mutations in protease and reverse transcriptase.</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>The HIV protease and reverse transcriptase genes were sequenced.</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Protease, Reverse transcriptase, Integrase</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="T124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>40431742</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RT,PR </t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>The protease and reverse-transcriptase regions of the HIV-1 pol gene were sequenced.</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>The paper reports sequencing of the HIV-1 pol gene, specifically the protease and reverse-transcriptase regions.</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="R125" t="n">
+        <v>1</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="T125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>40490983</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>The protease and reverse transcriptase genes were sequenced.</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>The paper mentions that the protease and reverse transcriptase genes were sequenced for resistance mutations.</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Protease, Reverse transcriptase</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>PR, RT.</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Unknown.</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="T126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>40573423</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>The genes sequenced included env, gag, and pol.</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>The paper reports sequencing of the envelope (env), gag, pol, protease, reverse transcriptase, and integrase genes.</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Env, Gag, Pol</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Capsid, CA; Envelope</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>env, gag, pol, protease, reverse transcriptase, and integrase</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Envelope, Gag, Pol</t>
+        </is>
+      </c>
+      <c r="R127" t="n">
+        <v>1</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>env, gag, pol</t>
+        </is>
+      </c>
+      <c r="T127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>40596906</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>The HIV pol region, specifically protease and reverse transcriptase genes, were sequenced.</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>The genes sequenced are the protease/reverse transcriptase (PR/RT) region of HIV.</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Protease, Reverse transcriptase</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Protease, Reverse transcriptase.</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="R128" t="n">
+        <v>1</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="T128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>40713598</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>The HIV-1 pol gene was sequenced.</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>The HIV-1 pol gene was sequenced.</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Reverse transcriptase, RT; Integrase, IN; Protease, PR.</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="R129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="T129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>40763144</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>The paper does not specify the exact HIV genes sequenced.</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>The paper mentions sequencing of mutations in the NRTI, NNRTI, PI, and INSTI genes, but it does not specify individual gene sequences.</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Reverse transcriptase, RT; Integrase, IN; Protease, PR</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Not reported.</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>40779404</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>The paper reports sequencing of the reverse transcriptase (RT), protease (PR), and integrase (IN) genes.</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>The HIV genes reported to have been sequenced include protease (PR), reverse transcriptase (RT), and integrase (IN).</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Protease, Reverse transcriptase, and Integrase.</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Reverse transcriptase, RT</t>
+        </is>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="T131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>40839365</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RT, IN </t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>The sequenced HIV genes include protease, reverse transcriptase, and integrase.</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Protease, reverse transcriptase, and integrase genes were sequenced.</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>1</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Protease (PR), reverse transcriptase (RT), and integrase (IN).</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="T132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>40857111</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Protease (PR), reverse transcriptase (RT), integrase (IN).</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>The paper reports sequencing of the protease (PR), reverse transcriptase (RT), and integrase (IN) genes.</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Protease, Reverse transcriptase, Integrase.</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>PR, RT, and IN</t>
+        </is>
+      </c>
+      <c r="T133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>40872801</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>The most commonly examined genes are those related to drug resistance mutations like reverse transcriptase and protease genes.</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>The paper reports sequencing of the RT and integrase gene.</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Unknown.</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>40938120</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>RT, PR</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>The pol gene was reported to have been sequenced.</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>The pol gene was sequenced.</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>PR, RT.</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>The HIV genes reported to have been sequenced are the protease (PR), reverse transcriptase (RT), and integrase (IN) genes.</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>PR and RT</t>
+        </is>
+      </c>
+      <c r="T135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>40938996</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>RT, IN, NC, Env</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>The genes reported to have been sequenced include Gag-Pol and Env-Nef regions.</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Env, NC, IN</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>NC, IN</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Gag-Pol, Env-Nef</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Capsid, CA; Envelope</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Gag-Pol, Env-Nef</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>NC, IN</t>
+        </is>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>40965168</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>The HIV-1 gag-protease DNA fragment was sequenced.</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>The paper reports sequencing of the capsid and reverse transcriptase genes.</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Capsid, CA</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Capsid, Reverse transcriptase</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>gag, protease</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Capsid, CA.</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Gag, PR, RT, CA</t>
+        </is>
+      </c>
+      <c r="R137" t="n">
+        <v>1</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>40974886</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>The genes sequenced include protease (PR), reverse transcriptase (RT), and integrase (IN).</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Protease (PR), reverse transcriptase (RT), and integrase (IN) were sequenced.</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>PR, RT, IN.</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>1</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Protease, Reverse transcriptase, Integrase.</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="R138" t="n">
+        <v>1</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="T138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>41004608</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>The main genes reported in this study were those involved in nonintegrase mutations, specifically the envelope (Env) and nucleocapsid (NC).</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>The paper reports sequencing of the entire HIV genome, including nonintegrase genes.</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Env, NC</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Full genome</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Full genome</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>All HIV genes (PR, RT, IN, Pol, CA, Env)</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Full genome.</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>All applicable gene targets (PR, RT, IN, Pol, CA, and Env)</t>
+        </is>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>41012586</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PR, RT, IN (presumably)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>The paper does not specify which HIV genes were sequenced.</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>The paper does not report sequencing of specific HIV genes.</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Not reported.</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="R140" t="n">
+        <v>1</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>41023944</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>RT,IN</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>The integrase gene was reported to have been sequenced.</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>The integrase gene was sequenced, and when available, mutations in the reverse transcriptase and protease regions were also analyzed.</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>IN, RT, Pol</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Integrase, IN.</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Integrase, IN</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Integrase, IN.</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Integrase</t>
+        </is>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Integrase</t>
+        </is>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>41029850</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RT, PR </t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>The sequenced HIV genes reported are the protease and reverse transcriptase genes.</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>HIV-1 protease and reverse-transcriptase genes were sequenced.</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT.</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="T142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>41056006</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>The HIV-1 capsid gene.</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>The paper mentions the sequencing of the HIV-1 capsid gene for resistance testing.</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Capsid, CA</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Capsid</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>CA (capsid)</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>1</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Full genome.</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Gag-Pro</t>
+        </is>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Capsid</t>
+        </is>
+      </c>
+      <c r="T143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>41057785</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RT,PR,IN</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>The paper reports mutations in the genes associated with drug classes including NRTIs, NNRTIs, PIs, and INSTIs.</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>The paper discusses mutations in several HIV genes, including those conferring resistance.</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Reverse transcriptase, RT</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>41088231</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Whole genome</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>The vif and env gene regions were reported to have been sequenced.</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>The sequenced genes include the near full-length genome (NFLG), specifically mentioning regions of vif and env genes, and the pol gene.</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Pol, Env</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Near full length genome</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Near full length genome</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Pol, Env</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Full genome.</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>PR, RT, IN, Pol, CA, Env</t>
+        </is>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>41091504</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>The sequenced gene mentioned is HIV-1 protease.</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>The paper does not report specific HIV genes that were sequenced.</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Protease, PR</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Protease (PR)</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>41093949</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>The specific HIV genes sequenced were in the Pol region.</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>The Pol region sequences were analyzed.</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>PR, RT</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Reverse transcriptase, RT</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Pol</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Protease, Reverse transcriptase, Integrase</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Pol</t>
+        </is>
+      </c>
+      <c r="T147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>41112839</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>The study reported the sequencing of the partial reverse transcriptase (RT) gene.</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>The partial reverse transcriptase (RT) gene was sequenced.</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Reverse transcriptase, RT</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Reverse transcriptase, RT.</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="R148" t="n">
+        <v>1</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="T148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>41129268</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>RT, PR, IN</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>The paper does not provide specific gene names sequenced, but mentions testing for drug resistance mutations across various antiretroviral drug classes.</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>The study focused on sequences relevant to drug resistance, particularly in the context of integrase inhibitors, protease inhibitors, NRTIs, NNRTIs, and integrase inhibitors.</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>NRTI, NNRTI, PI, INSTI</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>PR, RT, and possibly others.</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>41130593</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>RT,PR,IN,CA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>The HIV-1 capsid, protease, reverse transcriptase, and integrase genes were sequenced.</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>The HIV genes sequenced include capsid, protease, reverse transcriptase, and integrase.</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>PR, RT, IN, CA</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Capsid, CA</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>CA, PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>CA, PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>CA, PR, RT, IN.</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Capsid, Protease, Reverse transcriptase, Integrase</t>
+        </is>
+      </c>
+      <c r="R150" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>CA, PR, RT, and IN</t>
+        </is>
+      </c>
+      <c r="T150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>41140464</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>The HIV genes sequenced include the protease (PR), reverse transcriptase (RT), and integrase (IN) regions of the pol gene.</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>The HIV genes sequenced include those coding for Protease (PR), Reverse Transcriptase (RT), and Integrase (IN).</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>1</v>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>PR, RT, IN</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>PR, RT, and IN</t>
+        </is>
+      </c>
+      <c r="T151" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20251,7 +25047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T121"/>
+  <dimension ref="A1:T151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21107,9 +25903,13 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Tenofovir, Emtricitabine, Elvitegravir, Cobicistat</t>
+        </is>
+      </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -25143,7 +29943,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, ABC, EFV, DTG, LPV/r</t>
+        </is>
+      </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
@@ -26009,7 +30813,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
       <c r="T74" t="n">
         <v>0</v>
       </c>
@@ -27791,7 +32599,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dolutegravir, Rilpivirine, Lamivudine, Tenofovir, Efavirenz</t>
+          <t>Dolutegravir, Rilpivirine, Lamivudine, Tenofovir, Crizaline, Efavirenz</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -29661,6 +34469,2291 @@
         </is>
       </c>
       <c r="T121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>40391923</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, DTG, RAL</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Individuals primarily received tenofovir, lamivudine, and dolutegravir (TLD regimen).</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Individuals received tenofovir, lamivudine, and dolutegravir, and raltegravir.</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Tenofovir, Lamivudine, Dolutegravir</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Tenofovir, Lamivudine, Dolutegravir, Raltegravir</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Tenofovir (TFV), Lamivudine (3TC), Dolutagravir (DTG), Raltegravir (RAL)</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>DTG, tenofovir, lamivudine, dolutegravir</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>1</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Tenofovir, Lamivudine, and Dolutegravir.</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>40400229</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TDF, FTC</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Individuals received tenofovir disoproxil fumarate and emtricitabine (TDF/FTC) before sequencing.</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Specific drugs received included TDF, FTC, DTG, DRV, 3TC, ABC, and RAL, reflecting the treatments received prior to HIV sequencing.</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>TDF/FTC, bictegravir, dolutegravir, raltegravir, boosted darunavir, ABC, 3TC</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>1</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>TDF/TAF, FTC/3TC, bictegravir, darunavir, dolutegravir, raltegravir, ABC, rilpivirine</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Tenofovir disoproxil maleate, emtricitabine</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>1</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>The drugs received by individuals in the study before sample sequencing were bictegravir, boosted darunavir, dolutegravir, raltegravir, and rilpivirine.</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Tenofovir disoproxil fumarate (TDF), Emtricitabine (FTC)</t>
+        </is>
+      </c>
+      <c r="R123" t="n">
+        <v>1</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>TDF/TAF, FTC/3TC, bictegravir, boosted darunavir, dolutegravir, raltegravir</t>
+        </is>
+      </c>
+      <c r="T123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>40431710</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>AZT, ddI, d4T, 3TC, ABC, TDF, TAF, DLV, ETR, DOR, IDV, RTV, NFV, LPV, ATV, DRV, EVG, DTG, FOS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>The drugs included zidovudine, didanosine, tenofovir, darunavir, and others.</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Zidovudine (AZT), ritonavir (RTV), didanosine (ddI), abacavir (ABC), tenofovir disoproxil (TDF), lopinavir (LPV), etravirine (ETR), atazanavir (ATV), raltegravir (RAL), emtricitabine (FTC), dolutegravir (DTG), darunavir (DRV), and bictegravir (BIC).</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>AZT, 3TC, ddI, ABC, TDF, RTV, DRV, ETR, DTG, BIC, DOR</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>AZT, 3TC, TDF, DOR, RPV, DRV, ATV, BIC, RAL</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Zidovudine, Didanosine, Abacavir, Tenofovir, Lopinavir, Atazanavir, Darunavir, Raltegravir, Dolutegravir, Elvitegravir, Bictegravir, Rilpivirine, Doravirine</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>AZT, RTV, IDV, 3TC, DLV, ABC, NFV, EFV, TDF, LPV/r, ETR, ATV/r, PBO/RAL, DRV/r, RAL, DRV/c, DTG, FTC, EVG, BIC, RPV, DOR, FTR</t>
+        </is>
+      </c>
+      <c r="R124" t="n">
+        <v>1</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>AZT, RTV, ddI, ABC, TDF, LPV/r, ETR, RAL, DTG, DRV, BIC</t>
+        </is>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>40431742</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>No drugs were received by individuals prior to sample sequencing.</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>None, the study included treatment-naive individuals who had not received any ARV drugs.</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R125" t="n">
+        <v>1</v>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>40490983</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>AZT, 3TC, TDF, ABC, EFV, NVP, LPV, RTV, ATV (RTV is for boosting)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Drugs included atazanavir/ritonavir and lopinavir/ritonavir as part of second-line therapy.</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>The paper mentioned specific drugs such as atazanavir/ritonavir and lopinavir/ritonavir received prior to sequencing. The NRTIs lamivudine, zidovudine, and tenofovir were received before sequencing</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Efavirenz, Nevirapine, Atazanavir/Ritonavir, Lopinavir/Ritonavir</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>ABC, AZT, 3TC, TDF, ATV, LPV, EFV, NVP</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>ATV, LPV, DTG</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>EFV, NVP, ATV/r, LPV/r.</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>The drugs received by individuals in the study before sample sequencing include Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, and Lenacapavir (GS-6207).</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1</t>
+        </is>
+      </c>
+      <c r="R126" t="n">
+        <v>1</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>TDF/3TC/ATV/r, TDF/3TC/LPV/r, AZT/3TC/LPV/r, ABC/3TC/LPV/r, etc.
+Here are the answers in the requested format:</t>
+        </is>
+      </c>
+      <c r="T126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>40573423</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>No drugs were received as the individuals were ART-naïve.</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>The study included individuals who were ART-naïve at the time of sample sequencing, so they had not received any drugs before sequencing.</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>ATV/r, DRV/r, FPV/r, IDV/r, LPV/r, NFV, SQV/r, TPV/r, ABC, AZT, D4T, DDI, FTC, 3TC, TDF, DOR, EFV, ETR, NVP, RPV, BIC, CAB, DTG, EVG, RAL</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="n">
+        <v>1</v>
+      </c>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Lamivudine (3TC), Tenofovir (TFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>40596906</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>The drugs included zidovudine (ZDV), lamivudine (3TC), and nevirapine (NVP).</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Individuals in the study received zidovudine (ZDV), lamivudine (3TC), nevirapine (NVP), lopinavir/ritonavir, and efavirenz (EFV) before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV)</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV)</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>ZDV, 3TC, NVP, LPV, EFV</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>ZDV, 3TC, NVP, lopinavir/ritonavir, EFV</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Lopinavir/ritonavir, Efavirenz (EFV).</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Lopinavir/Ritonavir</t>
+        </is>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>ZDV, 3TC, EFV, NVP</t>
+        </is>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>40713598</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ABC, 3TC, AZT (ZDV), NVP, EFV</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Specific drugs included nevirapine (NVP), efavirenz (EFV), lamivudine (3TC), and zidovudine (ZDV).</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>The specific drugs received include Abacavir (ABC), Lamivudine (3TC), Nevirapine (NVP), Zidovudine (ZDV), and Efavirenz (EFV).</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine (ZDV), Lamivudine (3TC), Nevirapine (NVP), Efavirenz (EFV), Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>NVP, EFV, 3TC, ZDV, ABC, DTG</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Efavirenz (EFV), Nevirapine (NVP), Lamivudine (3TC)</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207).</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR)</t>
+        </is>
+      </c>
+      <c r="R129" t="n">
+        <v>1</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>ABC, 3TC, NVP, ZDV, 3TC, EFV</t>
+        </is>
+      </c>
+      <c r="T129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>40763144</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>AZT, ABC, 3TC, TDF, ATV, LPV, RTV, DTG</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Drugs received included TDF, 3TC, DTG, AZT, and others.</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>The study involved participants on various ART regimens including TDF/3TC/DTG, AZT/3TC/DTG, ABC/3TC/DTG, ABC/3TC/LPVr, TDF/3TC/ATVr, AZT/3TC/ATVr, and others before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Lamivudine (3TC), Tenofovir (TFV), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG)</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>ABC, AZT, 3TC, TDF, DTG, ATVr, LPVr</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>DTG, TDF, 3TC</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutegravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN).</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>40779404</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>TFV (no other ARVs specified; Data in supplementary methods)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Individuals received Tenofovir (TFV) and various classes including integrase inhibitors (INSTIs), non-nucleoside RT inhibitors (NNRTIs), and protease inhibitors (PIs).</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Participants received Tenofovir, INSTIs, NNRTIs, and PIs before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Tenofovir (TFV), Raltegravir, Elvitegravir, Dolutagravir, Bictegravir, Nevirapine, Delavirdine, Efavirenz, Etravirine, Rilpivirine, Doravirine, Amprenavir, Lopinavir, Atazanavir, Derunavir</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Tenofovir (TFV), INSTIs, NNRTIs, PIs</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>TFV, INSTIs, NNRTIs, and PIs.</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>TFV, INSTIs, NNRTIs, PIs</t>
+        </is>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>40839365</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DTG  </t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Specific drugs include abacavir, emtricitabine, and tenofovir.</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Individuals received drugs such as abacavir, emtricitabine, lamivudine, stavudine, tenofovir disoproxil fumarate, efavirenz, nevirapine, cabotegravir, and dolutegravir.</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG), Abacavir (ABC), Zidovudine'(AZT), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Efavirenz (EFV), Atazanavir (ATV), Derunavir (DRV)</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>The drugs received by individuals in the study before sample sequencing were abacavir (ABC), lamivudine (3TC), tenofovir disoproxil fumarate (TDF), efavirenz (EFV), and dolutegravir (DTG).</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine (AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine (FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Raltegravir (RAL), Elvitegravir (EVG), Dolutegravir (DTG), Bictegravir (BIC), Cabotegravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>40857111</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TAF, FTC, TDF, 3TC, DTG, BIC</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Dolutegravir, emtricitabine, tenofovir alafenamide, tenofovir disoproxil fumarate.</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>The drugs received include bictegravir, emtricitabine, tenofovir alafenamide, dolutegravir, and tenofovir disoproxil fumarate.</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Emtricitabine (FTC), Tenofovir (TFV), Dolutegravir (DTG), Bictegravir (BIC)</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Bictegravir (BIC), emtricitabine (FTC), tenofovir alafenamide (TAF), dolutegravir (DTG), emtricitabine (FTC), tenofovir disoproxil fumarate (TDF)</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Dolutegravir, emtricitabine, tenofovir disoproxil fumarate, bictegravir, emtricitabine, tenofovir alafenamide</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>1</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Bictegravir, Emtricitabine, Tenofovir alafenamide, Dolutegravir, Emtricitabine, Tenofovir disoproxil fumarate.</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Bictegravir, Emtricitabine, Tenofovir Alafenamide, Dolutegravir</t>
+        </is>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Bictegravir, Emtricitabine, Tenofovir Alafenamide, Dolutegravir, Emtricitabine, and Tenofovir Disoproxil Fumarate</t>
+        </is>
+      </c>
+      <c r="T133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>40872801</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Specific drugs include 3TC, FTC, AZT, and TDF among others.</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>The drugs received by individuals in the study include TDF, 3TC, DTG, FTC, AZT, and LPV/r.</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>3TC, FTC, AZT, TDF</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Tenofovir (TFV), Lamivudine (3TC), Efavirenz (EFV), Nevirapine (NVP), Lopinavir'(LPV), Ritonavir (RTV), Atazanavir (ATV), Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>3TC, FTC, AZT, TDF, EFV, NVP, DTG</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>The individuals in the study received the following drugs before sample sequencing: Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207).</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine (AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine (FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir (LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir (EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>40938120</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>No drugs were received, as all individuals were ART-naive before sampling.</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>None, individuals were ART-naive before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>NRTI (Nucleoside Reverse Transcriptase Inhibitor), including Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); NNRTI (Non-Nucleosid Reverse Transcriptase Inhibitor), including Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR); PI (Protease Inhibitor), including Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); INSTI (Integrase Inhibitor), including Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN); CAI (Capsid Inhibitor), including GS-CA1, Lenacapavir (GS-6207)</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>TDF, 3TC, EFV, NVP, D4T, AZT, LPV/r</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>None.</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>The individuals in the study received the following drugs before sample sequencing: Abacavir (ABC), Zidovudine (AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine (FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir (LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir (EVG), Dolutegravir (DTG), Bictegravir (BIC), Cabotegravir (CAB), Lenacapavir (LEN), GS-CA1.</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="n">
+        <v>1</v>
+      </c>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>40938996</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Individuals received dolutegravir (DTG) and possibly other INSTIs before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>DTG, RPV, LEN, CAB</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="n">
+        <v>1</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>DTG, RPV, CAB, RAL</t>
+        </is>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>40965168</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>No drugs were received by the individuals prior to sample sequencing.</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>The paper does not mention any drugs received by individuals in the study before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG), Tenofovir alafenamide (TAF), Efavirenz (EFV), Darunavir (DRV)</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>The drugs received by individuals in the study before sample sequencing are Raltegravir (RAL), Elvitegravir(EVG), Dolutegravir (DTG), Bictegravir (BIC), cabotegravir (CAB), Lenacapavir (LEN); Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV); Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV); Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR).</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>No drugs were received by individuals in the study before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="R137" t="n">
+        <v>1</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>40974886</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TAF, FTC, BIC</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Specific drugs are not detailed; only drug classes are mentioned.</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Bictegravir/emtricitabine/tenofovir alafenamide were received prior to sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir (TFV)</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Bictegravir (BIC), Emtricitabine (FTC), Tenofovir (TFV)</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Not reported.</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Bictegravir (BIC), cabotegravir (CAB), Emtricitabine (FTC), Tenofovir (TFV).</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="R138" t="n">
+        <v>1</v>
+      </c>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>41004608</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Participants received drugs like raltegravir, dolutegravir, elvitegravir or bictegravir.</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>The individuals in the study received raltegravir, dolutegravir, elvitegravir, or bictegravir before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC)</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>1</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207).</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Raltegravir, Dolutegravir, Elvitegravir, Bictegravir</t>
+        </is>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Raltegravir and dolutegravir</t>
+        </is>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>41012586</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>DTG, DRV/r</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>The specific drugs received by individuals are not listed in the study.</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>The paper does not provide specific drug names received by individuals before sequencing.</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG), Darunavir (DRV)</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>DTG, DRV</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Not reported.</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine (AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine (FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir (LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir (EVG), Dolutagravir (DTG), Bictegravir (BIC), Cabotegravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="R140" t="n">
+        <v>1</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>41023944</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>DTG (no other ARVs specified)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Drugs such as NRTIs and NNRTIs were received prior to sample sequencing.</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Specific drugs like Tenofovir, Lamivudine, Emtricitabine, Efavirenz were received by individuals in the study before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Not reported.</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>DTG</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN).</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>41029850</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>AZT, 3TC, ABC, TDF, EFV, NVP, ATV, RTV, LPV, DTG</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Drugs received included TDF, AZT, 3TC, EFV, NVP, and various PIs.</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Drugs received included ABC, 3TC, EFV, NVP, AZT, DTG, ATV/r, LPV/r, TDF.</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>ABC, 3TC, EFV, NVP, AZT, TDF, DTG, ATV/r, LPV/r</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Lamivudine (3TC), Tenofovir (TFV), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Dolutagravir (DTG)</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>ABC, AZT, TDF, 3TC, EFV, NVP, ATV, LPV, DTG</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>ABC, 3TC, EFV, NVP, TDF, AZT, DTG, ATV, LPV</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>ABC, AZT, EFV, NVP, TDF, 3TC, DTG, ATV, LPV, RAL, EVG, BIC, CAB, LEN, GS-CA1.</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine (AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine (FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir (LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV), Raltegravir (RAL), Elvitegravir (EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotegravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="R142" t="n">
+        <v>1</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>ABC, 3TC, EFV/NVP, AZT, TDF, DTG, ATV/r, LPV/r</t>
+        </is>
+      </c>
+      <c r="T142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>41056006</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>TAF, FTC, LEN, BIC</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>None; all were treatment-naive.</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Drugs received include lenacapavir, emtricitabine, tenofovir alafenamide, and bictegravir.</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Lenacapavir (LEN), Bictegravir (BIC), Emtricitabine (FTC), Tenofovir (TFV)</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>The drugs received by individuals in the study before sample sequencing are: Emtricitabine (FTC), Tenofovir (TFV), Lenacapavir (LEN), and Bictegravir (BIC).</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Emtricitabine (FTC), Tenofovir alafenamide (TAF), Bictegravir (BIC), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="R143" t="n">
+        <v>1</v>
+      </c>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>41057785</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ABC, AZT, D4T, TDF, ETR, NVP, EFV, LPV, DRV/r, DTG</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>The study participants received drugs like AZT, TDF, and other NRTIs and PIs.</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Specific drugs received included AZT, TDF, D4T, and TDF.</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>AZT, TDF, Efavirenz</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>AZT, TDF</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>AZT, D4T, TDF, ABC</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>AZT, TDF, NNRTIs</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>The drugs that were received by individuals in the study before sample sequencing are Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN).</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine (AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine (FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir (LPV), Atazanavir (ATV), Derunavir (DRV)</t>
+        </is>
+      </c>
+      <c r="R144" t="n">
+        <v>1</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>41088231</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>No drugs were received by individuals as they were ART-naive.</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>The individuals in the study had not received any drugs before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="n">
+        <v>1</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>BIC, FTC, and TAF.</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R145" t="n">
+        <v>1</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>41091504</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>The specific drugs received are not detailed in the paper.</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>The paper does not specify which drugs were received by individuals before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Derunavir (DRV)</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Derunavir (DRV)</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="n">
+        <v>1</v>
+      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>41093949</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>The paper does not list specific drugs received by individuals prior to sequencing.</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>The paper does not specify drugs received.</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Lamivudine (3TC), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Efavirenz (EFV), Etravirine (ETR)</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>AZT, 3TC, NVP, EFV, ETR</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutegravir (DTG), Bictegravir (BIC), cabotegravir (CAB), Lenacapavir (LEN), GS-CA1, Lenacapavir (GS-6207)</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>41112839</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>No drugs were received by individuals, as they were ART-naive.</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>All participants were ART-naive, so they had not received any drugs before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Not reported.</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="R148" t="n">
+        <v>1</v>
+      </c>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>41129268</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>AZT, 3TC, TDF, ABC, EFV, NVP, LPV/r, DTG</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Individuals received drugs including dolutegravir, lopinavir, nevirapine, efavirenz, abacavir, and zidovudine before sample sequencing.</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>The received drugs included DTG, ABC, AZT, TDF, LPV, 3TC, DRV, EFV, NVP, and ATV.</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Lamivudine (3TC), Tenofovir (TFV), Nevirapine (NVP), Efavirenz (EFV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Dolutagravir (DTG)</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>DTG, LPV, ABC, 3TC, TDF, AZT</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>DTG, ABC, AZT, TDF, LPV, and EFV.</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine (AZT), Lopinavir (LPV), Dolutegravir (DTG)</t>
+        </is>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>DTG, ABC, AZT, TDF, LPV, DRV, EFV, and NVP</t>
+        </is>
+      </c>
+      <c r="T149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>41130593</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>TDF, TAF, FTC, LEN</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Lenacapavir, emtricitabine/tenofovir alafenamide, and emtricitabine/tenofovir disoproxil fumarate.</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Specific drugs mentioned include emtricitabine, tenofovir, and dolutegravir, lamivudine.</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Emtricitabine (FTC), Tenofovir (TFV), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Emtricitabine/Tenofovir Alafenamide (F/TAF), Emtricitabine/Tenofovir Disoproxil Fumarate (F/TDF), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>lenacapavir, emtricitabine/tenofovir alafenamide, emtricitabine/tenofovir disoproxil fumarate</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>1</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>LEN, F/TAF, F/TDF.</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Emtricitabine, Tenofovir, Lenacapavir</t>
+        </is>
+      </c>
+      <c r="R150" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>41140464</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>The specific drugs are not listed, but high resistance was noted against nevirapine (NVP) and efavirenz (EFV).</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>The paper does not specify which drugs were received by individuals prior to sequencing.</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>The specific drugs received by individuals in the study before sample sequencing were Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN), GS-CA1, and Lenacapavir (GS-6207).</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Abacavir (ABC), Zidovudine (AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine (FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir (LPV), Atazanavir (ATV), Derunavir (DRV), Raltegravir (RAL), Elvitegravir (EVG), Dolutegravir (DTG), Bictegravir (BIC), Cabotegravir (CAB), Lenacapavir (LEN)</t>
+        </is>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Tenofovir, Lamivudine, Dolutegravir, Nevirapine, Efavirenz, Rilpivirine, Doravirine, Atazanavir, Lopinavir, Darunavir, Raltegravir, Elvitegravir, Cabotegravir, Lenacapavir, Maraviroc, Fostemsavir, Enfuvirtide, Ibalizumab</t>
+        </is>
+      </c>
+      <c r="T151" t="n">
         <v>0</v>
       </c>
     </row>
